--- a/experiment/Final Eksperimen/Model2/best_per_run.xlsx
+++ b/experiment/Final Eksperimen/Model2/best_per_run.xlsx
@@ -502,12 +502,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0.00000397</t>
+          <t>251820.00000000</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>296.77s</t>
+          <t>357.14s</t>
         </is>
       </c>
     </row>
@@ -526,12 +526,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>0.00000404</t>
+          <t>247830.00000000</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>262.22s</t>
+          <t>340.43s</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0.00000402</t>
+          <t>248970.00000000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>261.01s</t>
+          <t>340.36s</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0.00000394</t>
+          <t>254020.00000000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260.92s</t>
+          <t>315.45s</t>
         </is>
       </c>
     </row>
@@ -598,12 +598,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0.00000402</t>
+          <t>248750.00000000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280.84s</t>
+          <t>315.2s</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0.00000407</t>
+          <t>245640.00000000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>876.71s</t>
+          <t>932.66s</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0.00000404</t>
+          <t>247830.00000000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>894.31s</t>
+          <t>976.43s</t>
         </is>
       </c>
     </row>
@@ -670,12 +670,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0.00000402</t>
+          <t>248800.00000000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>899.37s</t>
+          <t>874.94s</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0.00000405</t>
+          <t>246750.00000000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>815.75s</t>
+          <t>901.47s</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0.00000409</t>
+          <t>244710.00000000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>783.94s</t>
+          <t>1048.16s</t>
         </is>
       </c>
     </row>
@@ -742,12 +742,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0.00000407</t>
+          <t>245640.00000000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1404.02s</t>
+          <t>1735.57s</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0.00000407</t>
+          <t>245650.00000000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1428.35s</t>
+          <t>1426.72s</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0.00000405</t>
+          <t>246840.00000000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1373.22s</t>
+          <t>1428.63s</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0.00000405</t>
+          <t>246750.00000000</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1304.9s</t>
+          <t>1425.82s</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0.00000409</t>
+          <t>244710.00000000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1348.18s</t>
+          <t>1425.37s</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0.00000407</t>
+          <t>245580.00000000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2826.04s</t>
+          <t>2868.13s</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0.00000407</t>
+          <t>245650.00000000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2715.54s</t>
+          <t>2881.79s</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0.00000405</t>
+          <t>246620.00000000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2713.77s</t>
+          <t>2852.21s</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0.00000409</t>
+          <t>244640.00000000</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2683.54s</t>
+          <t>2850.16s</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0.00000409</t>
+          <t>244710.00000000</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2843.38s</t>
+          <t>2818.22s</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0.00000408</t>
+          <t>244910.00000000</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>444.82s</t>
+          <t>466.27s</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0.00000400</t>
+          <t>249890.00000000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>445.63s</t>
+          <t>465.64s</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0.00000401</t>
+          <t>249570.00000000</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>454.3s</t>
+          <t>466.66s</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0.00000395</t>
+          <t>252970.00000000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>431.65s</t>
+          <t>468.33s</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0.00000400</t>
+          <t>249730.00000000</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>460.01s</t>
+          <t>466.06s</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0.00000408</t>
+          <t>244910.00000000</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1344.8s</t>
+          <t>1400.67s</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0.00000405</t>
+          <t>246760.00000000</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1432.93s</t>
+          <t>1405.78s</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0.00000404</t>
+          <t>247590.00000000</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1469.03s</t>
+          <t>1403.99s</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0.00000407</t>
+          <t>245800.00000000</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1311.07s</t>
+          <t>1401.89s</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0.00000413</t>
+          <t>241850.00000000</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1392.08s</t>
+          <t>1404.69s</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0.00000412</t>
+          <t>242860.00000000</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2365.04s</t>
+          <t>2340.71s</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0.00000410</t>
+          <t>243870.00000000</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2151.85s</t>
+          <t>2350.52s</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0.00000408</t>
+          <t>244890.00000000</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2270.32s</t>
+          <t>2350.13s</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0.00000411</t>
+          <t>243020.00000000</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2266.9s</t>
+          <t>2350.85s</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0.00000413</t>
+          <t>241850.00000000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2396.84s</t>
+          <t>2353.04s</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0.00000412</t>
+          <t>242860.00000000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4840.54s</t>
+          <t>5456.58s</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0.00000410</t>
+          <t>243870.00000000</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4540.32s</t>
+          <t>5162.38s</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0.00000414</t>
+          <t>241730.00000000</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4472.37s</t>
+          <t>5012.65s</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0.00000414</t>
+          <t>241760.00000000</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4575.86s</t>
+          <t>4528.49s</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>0.00000413</t>
+          <t>241850.00000000</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4498.68s</t>
+          <t>4586.81s</t>
         </is>
       </c>
     </row>
